--- a/cancellation_forms/049_debt_review_cancellation_form--cancellation_forms.xlsx
+++ b/cancellation_forms/049_debt_review_cancellation_form--cancellation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -669,8 +669,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -698,12 +698,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'cancel'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Cancel'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'continue'}</t>
+          <t>continue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Continue'}</t>
+          <t>Continue</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'error_in_debt_review_process'}</t>
+          <t>error_in_debt_review_process</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Error in debt review process'}</t>
+          <t>Error in debt review process</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'misrepresentation_by_debt_counselor'}</t>
+          <t>misrepresentation_by_debt_counselor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Misrepresentation by debt counselor'}</t>
+          <t>Misrepresentation by debt counselor</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'error_in_debt_review_process'}</t>
+          <t>error_in_debt_review_process</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Error in debt review process'}</t>
+          <t>Error in debt review process</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'misrepresentation_by_agency'}</t>
+          <t>misrepresentation_by_agency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Misrepresentation by agency'}</t>
+          <t>Misrepresentation by agency</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'cancel_debt_review'}</t>
+          <t>cancel_debt_review</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Cancel debt review'}</t>
+          <t>Cancel debt review</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'re-enroll_in_debt_review'}</t>
+          <t>re-enroll_in_debt_review</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Re-enroll in debt review'}</t>
+          <t>Re-enroll in debt review</t>
         </is>
       </c>
     </row>
